--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1142</v>
+        <v>1541</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>906</v>
+        <v>1196</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>463</v>
+        <v>627</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>396</v>
+        <v>507</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>438</v>
+        <v>578</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>249</v>
+        <v>347</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
@@ -1049,35 +1049,35 @@
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,32 +1141,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,47 +1307,47 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="J20" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,143 +1519,143 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L25" s="12" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J27" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1</v>
@@ -1739,35 +1739,35 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="J28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K28" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1789,35 +1789,35 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1846,13 +1846,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
@@ -1900,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>326</v>
+        <v>433</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>347</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.005763688760806916</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>120</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.4916666666666666</v>
+        <v>59</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>164</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.1951219512195122</v>
+        <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>353</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.0084985835694051</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>276</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.0108695652173913</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3076923076923077</v>
+        <v>36</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>106</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.01886792452830189</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>76</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.02631578947368421</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>9</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>55</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.01818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>31</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.03225806451612903</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>97</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.03092783505154639</v>
+        <v>3</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>16</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5625</v>
+        <v>9</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>26</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>42</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.09523809523809523</v>
+        <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1541</v>
+        <v>1637</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1196</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>578</v>
+        <v>626</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>2</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>59</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>55</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>32</v>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>3</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>3</v>
@@ -1103,16 +1103,16 @@
         <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J17" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K17" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="L17" s="12" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>2</v>
@@ -1310,13 +1310,13 @@
         <v>45</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>33</v>
@@ -1328,7 +1328,7 @@
         <v>12</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1364,25 +1364,25 @@
         <v>34</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>28</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>9</v>
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>5</v>
@@ -1436,7 +1436,7 @@
         <v>8</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1472,13 +1472,13 @@
         <v>32</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>22</v>
@@ -1490,7 +1490,7 @@
         <v>5</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>3</v>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>15</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>8</v>
@@ -1595,7 +1595,7 @@
         <v>9</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>16</v>
@@ -1634,13 +1634,13 @@
         <v>24</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>19</v>
@@ -1652,7 +1652,7 @@
         <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1666,50 +1666,50 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,50 +1720,50 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J28" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K28" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>2</v>
@@ -1810,14 +1810,14 @@
         <v>2</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1900,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -1782,7 +1782,11 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
@@ -1940,7 +1944,11 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
@@ -1990,7 +1998,11 @@
           <t>AMELIA</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>CHIODI ROBERTO</t>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1637</v>
+        <v>1731</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1262</v>
+        <v>1306</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>654</v>
+        <v>688</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="K11" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>2</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>59</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>95</v>
@@ -1001,13 +1001,13 @@
         <v>32</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>3</v>
@@ -1103,19 +1103,19 @@
         <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="J18" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K18" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="L18" s="12" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>16</v>
@@ -1265,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>14</v>
@@ -1274,10 +1274,10 @@
         <v>13</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>15</v>
@@ -1328,7 +1328,7 @@
         <v>12</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1580,13 +1580,13 @@
         <v>30</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>21</v>
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>9</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>30</v>
@@ -1649,10 +1649,10 @@
         <v>7</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1666,50 +1666,50 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,50 +1720,50 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1850,13 +1850,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1731</v>
+        <v>1842</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1306</v>
+        <v>1383</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>688</v>
+        <v>722</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>565</v>
+        <v>619</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>658</v>
+        <v>723</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>4</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
@@ -1049,35 +1049,35 @@
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>37</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>40</v>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>14</v>
@@ -1274,26 +1274,26 @@
         <v>13</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>1</v>
@@ -1598,10 +1598,10 @@
         <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1</v>
@@ -1760,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>2</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1850,13 +1850,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1842</v>
+        <v>1968</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1383</v>
+        <v>1465</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>722</v>
+        <v>773</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>3</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>60</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>4</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
@@ -1049,19 +1049,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>1</v>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>24</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         <v>95</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>6</v>
@@ -1220,7 +1220,7 @@
         <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>40</v>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>31</v>
@@ -1325,10 +1325,10 @@
         <v>7</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1364,13 +1364,13 @@
         <v>48</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>36</v>
@@ -1382,7 +1382,7 @@
         <v>12</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>2</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
         <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>14</v>
@@ -1436,7 +1436,7 @@
         <v>9</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>9</v>
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>1</v>
@@ -1490,7 +1490,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>4</v>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>1</v>
@@ -1580,7 +1580,7 @@
         <v>30</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>3</v>
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>21</v>
@@ -1649,10 +1649,10 @@
         <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1</v>
@@ -1720,108 +1720,108 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1850,13 +1850,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -1944,11 +1944,7 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
@@ -1998,11 +1994,7 @@
           <t>AMELIA</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>CHIODI ROBERTO</t>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N33" headerRowCount="1">
-  <autoFilter ref="A10:N33"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O33" headerRowCount="1">
+  <autoFilter ref="A10:O33"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA VITTORIO EMANUELE SNC - LOC.SPAZZAVENTO</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>628</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>481</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>751</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>359</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>437</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIALE BUOZZI 122/124</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>SS 222 KM 2+340 PONTE A EMA</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>133</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>71</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>71</v>
       </c>
       <c r="I13" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA ENRICO DE NICOLA 47/A - 47/B</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIALE NENNI 19 -21</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA UBALDINO PERUZZI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA SESTESE, 97/99</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIA DELLA RESISTENZA</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA DEL ROMITO</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>SS 71 KM.131+073</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>S.S.205 KM.52+330</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CHIODI ROBERTO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>VIALE BRACCI SNC</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,29 +1949,31 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>VIALE GRAMSCI 25</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" s="12" t="n">
         <v>0</v>
       </c>
@@ -1873,7 +1986,10 @@
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,29 +2008,31 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIALE ETRURIA, 403</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="12" t="n">
         <v>509</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" s="12" t="n">
         <v>0</v>
       </c>
@@ -1927,7 +2045,10 @@
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1944,21 +2065,23 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>VIALE CAMILLO BENSO DI CAVOUR</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
@@ -1977,7 +2100,10 @@
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1994,21 +2120,23 @@
           <t>AMELIA</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>VIA ROMA 48/A</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>CHIODI ROBERTO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
@@ -2027,7 +2155,10 @@
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O33" headerRowCount="1">
-  <autoFilter ref="A10:O33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O34" headerRowCount="1">
+  <autoFilter ref="A10:O34"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1968</v>
+        <v>2050</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1465</v>
+        <v>1525</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>773</v>
+        <v>815</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>751</v>
+        <v>800</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>3</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>213</v>
+      </c>
+      <c r="K12" s="12" t="n">
         <v>76</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>207</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>73</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>56</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>6</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>1</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>5</v>
@@ -1376,7 +1376,7 @@
         <v>52</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -1435,13 +1435,13 @@
         <v>48</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>36</v>
@@ -1453,7 +1453,7 @@
         <v>12</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>2</v>
@@ -1494,7 +1494,7 @@
         <v>43</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>9</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
         <v>21</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>4</v>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>34</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>8</v>
@@ -1630,10 +1630,10 @@
         <v>11</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,22 +1668,22 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>10</v>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>21</v>
@@ -1745,10 +1745,10 @@
         <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>41</v>
@@ -1798,19 +1798,19 @@
         <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,164 +1821,160 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIALE BRACCI SNC</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>VIALE BRACCI SNC</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>04840</t>
+          <t>07408</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BARBERINO DI MUGELLO</t>
+          <t>TERNI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE GRAMSCI 25</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>BORGO BOVIO S.S. 3</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>0</v>
@@ -1991,24 +1987,24 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>04840</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BARBERINO DI MUGELLO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIALE ETRURIA, 403</t>
+          <t>VIALE GRAMSCI 25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2025,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>312</v>
+        <v>207</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>509</v>
+        <v>53</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>0</v>
@@ -2057,36 +2053,40 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>53792</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIALE CAMILLO BENSO DI CAVOUR</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>VIALE ETRURIA, 403</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>2</v>
+        <v>351</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>
@@ -2105,30 +2105,30 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55442</t>
+          <t>53792</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>AMELIA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 48/A</t>
+          <t>VIALE CAMILLO BENSO DI CAVOUR</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
@@ -2159,6 +2159,61 @@
         <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>55442</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>AMELIA</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>VIA ROMA 48/A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>CHIODI ROBERTO</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2050</v>
+        <v>2187</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1525</v>
+        <v>1602</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>815</v>
+        <v>866</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>510</v>
+        <v>559</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>657</v>
+        <v>686</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>800</v>
+        <v>845</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>227</v>
+      </c>
+      <c r="K12" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>213</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>76</v>
-      </c>
       <c r="L12" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>61</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>33</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>455</v>
+        <v>484</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
         <v>42</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 71 KM.131+073</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>10</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>35</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>2</v>
@@ -1798,19 +1798,19 @@
         <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1925,14 +1925,14 @@
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1971,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2021,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2187</v>
+        <v>2308</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1602</v>
+        <v>1701</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>866</v>
+        <v>929</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>686</v>
+        <v>725</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>845</v>
+        <v>901</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>33</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>484</v>
+        <v>519</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,56 +1074,56 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>366</v>
+        <v>211</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,39 +1133,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>201</v>
+        <v>394</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>89</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H19" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="J19" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>2</v>
@@ -1435,7 +1435,7 @@
         <v>52</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>3</v>
@@ -1453,7 +1453,7 @@
         <v>21</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>1</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N22" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>160</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SS 71 KM.131+073</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>36</v>
+        <v>154</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>2</v>
@@ -1798,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>9</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>6</v>
@@ -1866,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1959,35 +1959,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2021,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>394</v>
+        <v>456</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>588</v>
+        <v>650</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2308</v>
+        <v>2393</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1701</v>
+        <v>1779</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>929</v>
+        <v>976</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>901</v>
+        <v>947</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>5</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>62</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>62</v>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>48</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>59</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>6</v>
@@ -1208,16 +1208,16 @@
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>8</v>
@@ -1376,13 +1376,13 @@
         <v>54</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>41</v>
@@ -1394,7 +1394,7 @@
         <v>13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>2</v>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>11</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>9</v>
@@ -1630,7 +1630,7 @@
         <v>12</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1671,7 +1671,7 @@
         <v>38</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>6</v>
@@ -1689,10 +1689,10 @@
         <v>10</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>2</v>
@@ -1798,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>9</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2393</v>
+        <v>2521</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1779</v>
+        <v>1889</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>976</v>
+        <v>1048</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>947</v>
+        <v>985</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>5</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>62</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,56 +1074,56 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>214</v>
+        <v>433</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,39 +1133,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
+        <v>207</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>413</v>
+        <v>226</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H19" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="M19" s="12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>8</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>7</v>
@@ -1571,10 +1571,10 @@
         <v>21</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>46</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>18</v>
@@ -1630,7 +1630,7 @@
         <v>12</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1644,118 +1644,118 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>38</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1980,14 +1980,14 @@
         <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>682</v>
+        <v>716</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2521</v>
+        <v>2694</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1889</v>
+        <v>2030</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1048</v>
+        <v>1151</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>774</v>
+        <v>807</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>592</v>
+        <v>638</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>985</v>
+        <v>1032</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>582</v>
+        <v>626</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>5</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>96</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>38</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,56 +1074,56 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>43</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>433</v>
+        <v>245</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,39 +1133,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>8</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="I23" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J23" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="M23" s="12" t="n">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>11</v>
@@ -1689,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1848,13 +1848,13 @@
         <v>28</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>17</v>
@@ -1866,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1904,22 +1904,22 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="K29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>2</v>
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>716</v>
+        <v>764</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2694</v>
+        <v>2879</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2030</v>
+        <v>2192</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1151</v>
+        <v>1267</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>696</v>
+        <v>762</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>807</v>
+        <v>845</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1032</v>
+        <v>1088</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>509</v>
+        <v>568</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>626</v>
+        <v>680</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="L12" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>223</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <v>65</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>216</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>64</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>38</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>17</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,56 +1074,56 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>215</v>
+        <v>3</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>245</v>
+        <v>479</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,39 +1133,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>460</v>
+        <v>257</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>8</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H20" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="M20" s="12" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="N21" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>146</v>
+        <v>211</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>65</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1671,10 +1671,10 @@
         <v>43</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>40</v>
@@ -1689,10 +1689,10 @@
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>41</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
@@ -1748,10 +1748,10 @@
         <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
@@ -1798,7 +1798,7 @@
         <v>12</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>11</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1848,13 +1848,13 @@
         <v>28</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>17</v>
@@ -1866,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1904,22 +1904,22 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>2</v>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>5</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>3</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>764</v>
+        <v>807</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MOSCA FRANCESCO.xlsx
@@ -684,13 +684,13 @@
         <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2879</v>
+        <v>2893</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2192</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1267</v>
+        <v>1234</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>845</v>
+        <v>821</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1088</v>
+        <v>1056</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>240</v>
@@ -863,7 +863,7 @@
         <v>198</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>65</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>128</v>
@@ -922,10 +922,10 @@
         <v>73</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>108</v>
@@ -972,7 +972,7 @@
         <v>101</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>87</v>
@@ -981,7 +981,7 @@
         <v>33</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>38</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>52</v>
@@ -1040,7 +1040,7 @@
         <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>17</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>12</v>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>45</v>
@@ -1099,7 +1099,7 @@
         <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>15</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>46</v>
@@ -1158,7 +1158,7 @@
         <v>46</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>15</v>
@@ -1208,7 +1208,7 @@
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>37</v>
@@ -1217,14 +1217,14 @@
         <v>57</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>58</v>
@@ -1276,7 +1276,7 @@
         <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>82</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>42</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>33</v>
@@ -1335,7 +1335,7 @@
         <v>27</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>8</v>
@@ -1385,7 +1385,7 @@
         <v>24</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>17</v>
@@ -1394,7 +1394,7 @@
         <v>22</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
@@ -1435,16 +1435,16 @@
         <v>67</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>24</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>9</v>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
         <v>66</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="N22" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1644,118 +1644,118 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L25" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L25" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M25" s="12" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>11</v>
@@ -1848,7 +1848,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>4</v>
@@ -1857,7 +1857,7 @@
         <v>26</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>5</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>5</v>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>5</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
